--- a/5/search/FY5_Missile2_results/fine_tuned/all_fine_tuned_solutions.xlsx
+++ b/5/search/FY5_Missile2_results/fine_tuned/all_fine_tuned_solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,37 +492,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116.2</v>
+        <v>117</v>
       </c>
       <c r="B2" t="n">
-        <v>131.9</v>
+        <v>130.4</v>
       </c>
       <c r="C2" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>11846.95448473202</v>
+        <v>11815.99277667926</v>
       </c>
       <c r="F2" t="n">
-        <v>343.2979034088698</v>
+        <v>323.7450150832633</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>11823.66063593873</v>
+        <v>11780.47255997964</v>
       </c>
       <c r="I2" t="n">
-        <v>390.6372549928873</v>
+        <v>393.4573655357614</v>
       </c>
       <c r="J2" t="n">
-        <v>1299.216</v>
+        <v>1298.236</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3999999999999986</v>
+        <v>0.6000000000000014</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -530,37 +530,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116.2</v>
+        <v>117</v>
       </c>
       <c r="B3" t="n">
-        <v>131.9</v>
+        <v>130.4</v>
       </c>
       <c r="C3" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>11823.66063593873</v>
+        <v>11780.47255997964</v>
       </c>
       <c r="F3" t="n">
-        <v>390.6372549928874</v>
+        <v>393.4573655357617</v>
       </c>
       <c r="G3" t="n">
         <v>1300</v>
       </c>
       <c r="H3" t="n">
-        <v>11823.66063593873</v>
+        <v>11780.47255997964</v>
       </c>
       <c r="I3" t="n">
-        <v>390.6372549928874</v>
+        <v>393.4573655357617</v>
       </c>
       <c r="J3" t="n">
         <v>1300</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5999999999999979</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -568,37 +568,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116.2</v>
+        <v>117</v>
       </c>
       <c r="B4" t="n">
-        <v>134.9</v>
+        <v>131.4</v>
       </c>
       <c r="C4" t="n">
         <v>19.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>11844.55269289284</v>
+        <v>11842.70557768394</v>
       </c>
       <c r="F4" t="n">
-        <v>348.1789889398979</v>
+        <v>271.3181912000196</v>
       </c>
       <c r="G4" t="n">
         <v>1300</v>
       </c>
       <c r="H4" t="n">
-        <v>11820.72903707619</v>
+        <v>11783.05122601816</v>
       </c>
       <c r="I4" t="n">
-        <v>396.5950505675245</v>
+        <v>388.3964484783711</v>
       </c>
       <c r="J4" t="n">
-        <v>1299.216</v>
+        <v>1295.1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1000000000000014</v>
+        <v>0.5999999999999979</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -606,37 +606,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116.2</v>
+        <v>117</v>
       </c>
       <c r="B5" t="n">
-        <v>134.9</v>
+        <v>131.4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>11820.72903707619</v>
+        <v>11806.91296668447</v>
       </c>
       <c r="F5" t="n">
-        <v>396.595050567525</v>
+        <v>341.5651455670309</v>
       </c>
       <c r="G5" t="n">
         <v>1300</v>
       </c>
       <c r="H5" t="n">
-        <v>11820.72903707619</v>
+        <v>11783.05122601816</v>
       </c>
       <c r="I5" t="n">
-        <v>396.595050567525</v>
+        <v>388.3964484783713</v>
       </c>
       <c r="J5" t="n">
-        <v>1300</v>
+        <v>1299.216</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3000000000000007</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -644,37 +644,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116.2</v>
+        <v>117</v>
       </c>
       <c r="B6" t="n">
-        <v>135.9</v>
+        <v>132.4</v>
       </c>
       <c r="C6" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
         <v>0.2</v>
       </c>
       <c r="E6" t="n">
-        <v>11835.98747934868</v>
+        <v>11797.83315668968</v>
       </c>
       <c r="F6" t="n">
-        <v>365.5858013115799</v>
+        <v>359.3852760507984</v>
       </c>
       <c r="G6" t="n">
         <v>1300</v>
       </c>
       <c r="H6" t="n">
-        <v>11823.9873502698</v>
+        <v>11785.81148825658</v>
       </c>
       <c r="I6" t="n">
-        <v>389.973283799328</v>
+        <v>382.9791288113063</v>
       </c>
       <c r="J6" t="n">
         <v>1299.804</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>2.199999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -682,37 +682,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B7" t="n">
-        <v>131.9</v>
+        <v>134.4</v>
       </c>
       <c r="C7" t="n">
         <v>19.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>11806.58188149987</v>
+        <v>11816.2833305991</v>
       </c>
       <c r="F7" t="n">
-        <v>263.5188742388696</v>
+        <v>323.1747709077831</v>
       </c>
       <c r="G7" t="n">
         <v>1300</v>
       </c>
       <c r="H7" t="n">
-        <v>11745.06548363903</v>
+        <v>11779.6735367001</v>
       </c>
       <c r="I7" t="n">
-        <v>380.1951048697391</v>
+        <v>395.0255370183333</v>
       </c>
       <c r="J7" t="n">
-        <v>1295.1</v>
+        <v>1298.236</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -720,37 +720,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B8" t="n">
-        <v>131.9</v>
+        <v>134.4</v>
       </c>
       <c r="C8" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>11781.97532235553</v>
+        <v>11779.6735367001</v>
       </c>
       <c r="F8" t="n">
-        <v>310.1893664912177</v>
+        <v>395.0255370183331</v>
       </c>
       <c r="G8" t="n">
         <v>1300</v>
       </c>
       <c r="H8" t="n">
-        <v>11745.06548363903</v>
+        <v>11779.6735367001</v>
       </c>
       <c r="I8" t="n">
-        <v>380.1951048697396</v>
+        <v>395.0255370183331</v>
       </c>
       <c r="J8" t="n">
-        <v>1298.236</v>
+        <v>1300</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -758,37 +758,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B9" t="n">
-        <v>131.9</v>
+        <v>135.4</v>
       </c>
       <c r="C9" t="n">
-        <v>20.2</v>
+        <v>18.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>11757.3687632112</v>
+        <v>11844.35810310299</v>
       </c>
       <c r="F9" t="n">
-        <v>356.8598587435654</v>
+        <v>268.0749274519744</v>
       </c>
       <c r="G9" t="n">
         <v>1300</v>
       </c>
       <c r="H9" t="n">
-        <v>11745.06548363903</v>
+        <v>11782.88778943825</v>
       </c>
       <c r="I9" t="n">
-        <v>380.1951048697392</v>
+        <v>388.7172108270794</v>
       </c>
       <c r="J9" t="n">
-        <v>1299.804</v>
+        <v>1295.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.300000000000001</v>
+        <v>0.4000000000000021</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -796,37 +796,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B10" t="n">
-        <v>132.9</v>
+        <v>135.4</v>
       </c>
       <c r="C10" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="D10" t="n">
         <v>0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>11772.7408668768</v>
+        <v>11807.47591490415</v>
       </c>
       <c r="F10" t="n">
-        <v>327.7040698004762</v>
+        <v>340.4602974770373</v>
       </c>
       <c r="G10" t="n">
         <v>1300</v>
       </c>
       <c r="H10" t="n">
-        <v>11747.94775307634</v>
+        <v>11782.88778943825</v>
       </c>
       <c r="I10" t="n">
-        <v>374.7283944429099</v>
+        <v>388.7172108270792</v>
       </c>
       <c r="J10" t="n">
         <v>1299.216</v>
       </c>
       <c r="K10" t="n">
-        <v>1.899999999999999</v>
+        <v>1.699999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -834,37 +834,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B11" t="n">
-        <v>132.9</v>
+        <v>136.4</v>
       </c>
       <c r="C11" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="E11" t="n">
-        <v>11772.7408668768</v>
+        <v>11798.6684992092</v>
       </c>
       <c r="F11" t="n">
-        <v>327.7040698004762</v>
+        <v>357.7458240462915</v>
       </c>
       <c r="G11" t="n">
         <v>1300</v>
       </c>
       <c r="H11" t="n">
-        <v>11735.5511961761</v>
+        <v>11786.28363837631</v>
       </c>
       <c r="I11" t="n">
-        <v>398.2405567641272</v>
+        <v>382.0524820261501</v>
       </c>
       <c r="J11" t="n">
-        <v>1298.236</v>
+        <v>1299.804</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09999999999999787</v>
+        <v>0.5999999999999979</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -872,37 +872,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B12" t="n">
-        <v>132.9</v>
+        <v>137.4</v>
       </c>
       <c r="C12" t="n">
-        <v>20.2</v>
+        <v>18.8</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
-        <v>11747.94775307633</v>
+        <v>11827.28806031278</v>
       </c>
       <c r="F12" t="n">
-        <v>374.72839444291</v>
+        <v>301.5767727614571</v>
       </c>
       <c r="G12" t="n">
         <v>1300</v>
       </c>
       <c r="H12" t="n">
-        <v>11747.94775307633</v>
+        <v>11777.38542458141</v>
       </c>
       <c r="I12" t="n">
-        <v>374.72839444291</v>
+        <v>399.5162099002425</v>
       </c>
       <c r="J12" t="n">
-        <v>1300</v>
+        <v>1296.864</v>
       </c>
       <c r="K12" t="n">
-        <v>2.299999999999997</v>
+        <v>0.1000000000000014</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -910,37 +910,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B13" t="n">
-        <v>133.9</v>
+        <v>137.4</v>
       </c>
       <c r="C13" t="n">
         <v>19.4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E13" t="n">
-        <v>11788.48607985468</v>
+        <v>11789.86108351425</v>
       </c>
       <c r="F13" t="n">
-        <v>297.8406160772147</v>
+        <v>375.0313506155458</v>
       </c>
       <c r="G13" t="n">
         <v>1300</v>
       </c>
       <c r="H13" t="n">
-        <v>11738.52674294147</v>
+        <v>11777.38542458141</v>
       </c>
       <c r="I13" t="n">
-        <v>392.5969301422546</v>
+        <v>399.516209900242</v>
       </c>
       <c r="J13" t="n">
-        <v>1296.864</v>
+        <v>1299.804</v>
       </c>
       <c r="K13" t="n">
-        <v>1.299999999999997</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -948,37 +948,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B14" t="n">
-        <v>133.9</v>
+        <v>138.4</v>
       </c>
       <c r="C14" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>11763.50641139807</v>
+        <v>11818.75303891768</v>
       </c>
       <c r="F14" t="n">
-        <v>345.2187731097351</v>
+        <v>318.3276954161984</v>
       </c>
       <c r="G14" t="n">
         <v>1300</v>
       </c>
       <c r="H14" t="n">
-        <v>11738.52674294147</v>
+        <v>11781.05366781931</v>
       </c>
       <c r="I14" t="n">
-        <v>392.5969301422548</v>
+        <v>392.3168771848006</v>
       </c>
       <c r="J14" t="n">
-        <v>1299.216</v>
+        <v>1298.236</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -986,37 +986,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B15" t="n">
-        <v>133.9</v>
+        <v>138.4</v>
       </c>
       <c r="C15" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>11738.52674294147</v>
+        <v>11781.05366781931</v>
       </c>
       <c r="F15" t="n">
-        <v>392.5969301422547</v>
+        <v>392.3168771848</v>
       </c>
       <c r="G15" t="n">
         <v>1300</v>
       </c>
       <c r="H15" t="n">
-        <v>11738.52674294147</v>
+        <v>11781.05366781931</v>
       </c>
       <c r="I15" t="n">
-        <v>392.5969301422547</v>
+        <v>392.3168771848</v>
       </c>
       <c r="J15" t="n">
         <v>1300</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5</v>
+        <v>1.699999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1024,37 +1024,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117.8</v>
+        <v>117</v>
       </c>
       <c r="B16" t="n">
-        <v>134.9</v>
+        <v>139.4</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E16" t="n">
-        <v>11804.60440214483</v>
+        <v>11810.21801752257</v>
       </c>
       <c r="F16" t="n">
-        <v>267.2694975737818</v>
+        <v>335.0786180709397</v>
       </c>
       <c r="G16" t="n">
         <v>1300</v>
       </c>
       <c r="H16" t="n">
-        <v>11741.68884436297</v>
+        <v>11784.9035072571</v>
       </c>
       <c r="I16" t="n">
-        <v>386.5994711302966</v>
+        <v>384.7611418596829</v>
       </c>
       <c r="J16" t="n">
-        <v>1295.1</v>
+        <v>1299.216</v>
       </c>
       <c r="K16" t="n">
-        <v>1.900000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1062,37 +1062,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B17" t="n">
-        <v>134.9</v>
+        <v>129.4</v>
       </c>
       <c r="C17" t="n">
         <v>19.4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6000000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="E17" t="n">
-        <v>11779.43817903208</v>
+        <v>11798.31110750022</v>
       </c>
       <c r="F17" t="n">
-        <v>315.0014869963875</v>
+        <v>204.0533421953851</v>
       </c>
       <c r="G17" t="n">
         <v>1300</v>
       </c>
       <c r="H17" t="n">
-        <v>11741.68884436297</v>
+        <v>11699.20274523219</v>
       </c>
       <c r="I17" t="n">
-        <v>386.5994711302965</v>
+        <v>385.8309374279943</v>
       </c>
       <c r="J17" t="n">
-        <v>1298.236</v>
+        <v>1287.456</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>0.9000000000000021</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1100,37 +1100,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B18" t="n">
-        <v>134.9</v>
+        <v>129.4</v>
       </c>
       <c r="C18" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>11754.27195591934</v>
+        <v>11761.14547164971</v>
       </c>
       <c r="F18" t="n">
-        <v>362.7334764189936</v>
+        <v>272.2199404076136</v>
       </c>
       <c r="G18" t="n">
         <v>1300</v>
       </c>
       <c r="H18" t="n">
-        <v>11741.68884436297</v>
+        <v>11699.2027452322</v>
       </c>
       <c r="I18" t="n">
-        <v>386.5994711302965</v>
+        <v>385.8309374279943</v>
       </c>
       <c r="J18" t="n">
-        <v>1299.804</v>
+        <v>1295.1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.700000000000003</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1138,37 +1138,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B19" t="n">
-        <v>135.9</v>
+        <v>129.4</v>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>20.6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E19" t="n">
-        <v>11795.74305597837</v>
+        <v>11723.9798357992</v>
       </c>
       <c r="F19" t="n">
-        <v>284.0765361028684</v>
+        <v>340.3865386198422</v>
       </c>
       <c r="G19" t="n">
         <v>1300</v>
       </c>
       <c r="H19" t="n">
-        <v>11745.03750044061</v>
+        <v>11711.5912905157</v>
       </c>
       <c r="I19" t="n">
-        <v>380.2481797282525</v>
+        <v>363.1087380239182</v>
       </c>
       <c r="J19" t="n">
-        <v>1296.864</v>
+        <v>1299.804</v>
       </c>
       <c r="K19" t="n">
-        <v>1.899999999999999</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1176,37 +1176,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B20" t="n">
-        <v>135.9</v>
+        <v>129.4</v>
       </c>
       <c r="C20" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="D20" t="n">
         <v>0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>11770.39027820949</v>
+        <v>11723.9798357992</v>
       </c>
       <c r="F20" t="n">
-        <v>332.1623579155603</v>
+        <v>340.3865386198422</v>
       </c>
       <c r="G20" t="n">
         <v>1300</v>
       </c>
       <c r="H20" t="n">
-        <v>11745.03750044061</v>
+        <v>11699.20274523219</v>
       </c>
       <c r="I20" t="n">
-        <v>380.2481797282521</v>
+        <v>385.8309374279943</v>
       </c>
       <c r="J20" t="n">
         <v>1299.216</v>
       </c>
       <c r="K20" t="n">
-        <v>2.800000000000001</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1214,37 +1214,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B21" t="n">
-        <v>135.9</v>
+        <v>130.4</v>
       </c>
       <c r="C21" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
-        <v>11745.03750044061</v>
+        <v>11789.02448545617</v>
       </c>
       <c r="F21" t="n">
-        <v>380.2481797282526</v>
+        <v>221.0862119186877</v>
       </c>
       <c r="G21" t="n">
         <v>1300</v>
       </c>
       <c r="H21" t="n">
-        <v>11745.03750044061</v>
+        <v>11701.63449987053</v>
       </c>
       <c r="I21" t="n">
-        <v>380.2481797282526</v>
+        <v>381.3707839128197</v>
       </c>
       <c r="J21" t="n">
-        <v>1300</v>
+        <v>1290.396</v>
       </c>
       <c r="K21" t="n">
-        <v>3.100000000000001</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1252,37 +1252,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B22" t="n">
-        <v>136.9</v>
+        <v>130.4</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" t="n">
         <v>0.8</v>
       </c>
       <c r="E22" t="n">
-        <v>11786.88170981191</v>
+        <v>11751.5716344909</v>
       </c>
       <c r="F22" t="n">
-        <v>300.8835746319551</v>
+        <v>289.7795999161731</v>
       </c>
       <c r="G22" t="n">
         <v>1300</v>
       </c>
       <c r="H22" t="n">
-        <v>11735.80304496188</v>
+        <v>11701.63449987053</v>
       </c>
       <c r="I22" t="n">
-        <v>397.7628830375112</v>
+        <v>381.3707839128201</v>
       </c>
       <c r="J22" t="n">
         <v>1296.864</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6000000000000014</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1290,37 +1290,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B23" t="n">
-        <v>136.9</v>
+        <v>130.4</v>
       </c>
       <c r="C23" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>11761.3423773869</v>
+        <v>11714.11878352562</v>
       </c>
       <c r="F23" t="n">
-        <v>349.3232288347331</v>
+        <v>358.4729879136585</v>
       </c>
       <c r="G23" t="n">
         <v>1300</v>
       </c>
       <c r="H23" t="n">
-        <v>11735.80304496188</v>
+        <v>11701.63449987053</v>
       </c>
       <c r="I23" t="n">
-        <v>397.7628830375109</v>
+        <v>381.3707839128201</v>
       </c>
       <c r="J23" t="n">
-        <v>1299.216</v>
+        <v>1299.804</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8000000000000007</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1328,37 +1328,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B24" t="n">
-        <v>136.9</v>
+        <v>131.4</v>
       </c>
       <c r="C24" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E24" t="n">
-        <v>11735.80304496188</v>
+        <v>11779.73786341212</v>
       </c>
       <c r="F24" t="n">
-        <v>397.7628830375111</v>
+        <v>238.1190816419908</v>
       </c>
       <c r="G24" t="n">
         <v>1300</v>
       </c>
       <c r="H24" t="n">
-        <v>11735.80304496188</v>
+        <v>11704.25773125205</v>
       </c>
       <c r="I24" t="n">
-        <v>397.7628830375111</v>
+        <v>376.5594372074746</v>
       </c>
       <c r="J24" t="n">
-        <v>1300</v>
+        <v>1292.944</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8000000000000007</v>
+        <v>2.399999999999999</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1366,37 +1366,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B25" t="n">
-        <v>131.9</v>
+        <v>131.4</v>
       </c>
       <c r="C25" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>11717.94593898363</v>
+        <v>11741.99779733209</v>
       </c>
       <c r="F25" t="n">
-        <v>275.2794133977095</v>
+        <v>307.339259424733</v>
       </c>
       <c r="G25" t="n">
         <v>1300</v>
       </c>
       <c r="H25" t="n">
-        <v>11666.14577490216</v>
+        <v>11704.25773125205</v>
       </c>
       <c r="I25" t="n">
-        <v>367.209894747112</v>
+        <v>376.5594372074751</v>
       </c>
       <c r="J25" t="n">
-        <v>1296.864</v>
+        <v>1298.236</v>
       </c>
       <c r="K25" t="n">
-        <v>1.800000000000001</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1404,37 +1404,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B26" t="n">
-        <v>131.9</v>
+        <v>131.4</v>
       </c>
       <c r="C26" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>11717.94593898363</v>
+        <v>11704.25773125205</v>
       </c>
       <c r="F26" t="n">
-        <v>275.2794133977095</v>
+        <v>376.5594372074752</v>
       </c>
       <c r="G26" t="n">
         <v>1300</v>
       </c>
       <c r="H26" t="n">
-        <v>11653.19573388179</v>
+        <v>11704.25773125205</v>
       </c>
       <c r="I26" t="n">
-        <v>390.1925150844625</v>
+        <v>376.5594372074752</v>
       </c>
       <c r="J26" t="n">
-        <v>1295.1</v>
+        <v>1300</v>
       </c>
       <c r="K26" t="n">
-        <v>1.100000000000001</v>
+        <v>3.299999999999997</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1442,37 +1442,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B27" t="n">
-        <v>131.9</v>
+        <v>132.4</v>
       </c>
       <c r="C27" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>11692.04585694289</v>
+        <v>11770.45124136807</v>
       </c>
       <c r="F27" t="n">
-        <v>321.2446540724104</v>
+        <v>255.1519513652938</v>
       </c>
       <c r="G27" t="n">
         <v>1300</v>
       </c>
       <c r="H27" t="n">
-        <v>11666.14577490216</v>
+        <v>11707.07243937674</v>
       </c>
       <c r="I27" t="n">
-        <v>367.2098947471114</v>
+        <v>371.3968973119585</v>
       </c>
       <c r="J27" t="n">
-        <v>1299.216</v>
+        <v>1295.1</v>
       </c>
       <c r="K27" t="n">
-        <v>1.700000000000003</v>
+        <v>1.5</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1480,37 +1480,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B28" t="n">
-        <v>131.9</v>
+        <v>132.4</v>
       </c>
       <c r="C28" t="n">
-        <v>20.6</v>
+        <v>19.4</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
-        <v>11666.14577490216</v>
+        <v>11770.45124136807</v>
       </c>
       <c r="F28" t="n">
-        <v>367.2098947471118</v>
+        <v>255.1519513652938</v>
       </c>
       <c r="G28" t="n">
         <v>1300</v>
       </c>
       <c r="H28" t="n">
-        <v>11666.14577490216</v>
+        <v>11694.39667897847</v>
       </c>
       <c r="I28" t="n">
-        <v>367.2098947471118</v>
+        <v>394.6458865012913</v>
       </c>
       <c r="J28" t="n">
-        <v>1300</v>
+        <v>1292.944</v>
       </c>
       <c r="K28" t="n">
-        <v>1.700000000000003</v>
+        <v>0.5</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1518,37 +1518,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B29" t="n">
-        <v>132.9</v>
+        <v>132.4</v>
       </c>
       <c r="C29" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="n">
-        <v>11734.32248820423</v>
+        <v>11732.42396017327</v>
       </c>
       <c r="F29" t="n">
-        <v>246.2157206587394</v>
+        <v>324.8989189332924</v>
       </c>
       <c r="G29" t="n">
         <v>1300</v>
       </c>
       <c r="H29" t="n">
-        <v>11669.08137934877</v>
+        <v>11707.07243937674</v>
       </c>
       <c r="I29" t="n">
-        <v>362.0000361566126</v>
+        <v>371.3968973119581</v>
       </c>
       <c r="J29" t="n">
-        <v>1295.1</v>
+        <v>1299.216</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2000000000000028</v>
+        <v>2.299999999999997</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1556,37 +1556,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B30" t="n">
-        <v>132.9</v>
+        <v>132.4</v>
       </c>
       <c r="C30" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D30" t="n">
         <v>0.6000000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>11708.22604466205</v>
+        <v>11732.42396017327</v>
       </c>
       <c r="F30" t="n">
-        <v>292.5294468578891</v>
+        <v>324.8989189332924</v>
       </c>
       <c r="G30" t="n">
         <v>1300</v>
       </c>
       <c r="H30" t="n">
-        <v>11669.08137934877</v>
+        <v>11694.39667897847</v>
       </c>
       <c r="I30" t="n">
-        <v>362.0000361566131</v>
+        <v>394.6458865012913</v>
       </c>
       <c r="J30" t="n">
         <v>1298.236</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7000000000000028</v>
+        <v>0.3000000000000007</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1594,37 +1594,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B31" t="n">
-        <v>132.9</v>
+        <v>133.4</v>
       </c>
       <c r="C31" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="E31" t="n">
-        <v>11708.22604466205</v>
+        <v>11799.47911563359</v>
       </c>
       <c r="F31" t="n">
-        <v>292.5294468578891</v>
+        <v>201.911063735341</v>
       </c>
       <c r="G31" t="n">
         <v>1300</v>
       </c>
       <c r="H31" t="n">
-        <v>11656.03315757768</v>
+        <v>11697.30712547475</v>
       </c>
       <c r="I31" t="n">
-        <v>385.1568992561877</v>
+        <v>389.3077500106893</v>
       </c>
       <c r="J31" t="n">
-        <v>1296.864</v>
+        <v>1287.456</v>
       </c>
       <c r="K31" t="n">
-        <v>2.600000000000001</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1632,37 +1632,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B32" t="n">
-        <v>132.9</v>
+        <v>133.4</v>
       </c>
       <c r="C32" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>11682.12960111986</v>
+        <v>11761.16461932403</v>
       </c>
       <c r="F32" t="n">
-        <v>338.8431730570383</v>
+        <v>272.1848210885964</v>
       </c>
       <c r="G32" t="n">
         <v>1300</v>
       </c>
       <c r="H32" t="n">
-        <v>11669.08137934877</v>
+        <v>11697.30712547475</v>
       </c>
       <c r="I32" t="n">
-        <v>362.0000361566128</v>
+        <v>389.3077500106891</v>
       </c>
       <c r="J32" t="n">
-        <v>1299.804</v>
+        <v>1295.1</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7000000000000028</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1670,37 +1670,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B33" t="n">
-        <v>132.9</v>
+        <v>133.4</v>
       </c>
       <c r="C33" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E33" t="n">
-        <v>11682.12960111986</v>
+        <v>11722.85012301446</v>
       </c>
       <c r="F33" t="n">
-        <v>338.8431730570383</v>
+        <v>342.4585784418523</v>
       </c>
       <c r="G33" t="n">
         <v>1300</v>
       </c>
       <c r="H33" t="n">
-        <v>11656.03315757768</v>
+        <v>11710.07862424461</v>
       </c>
       <c r="I33" t="n">
-        <v>385.1568992561874</v>
+        <v>365.8831642262708</v>
       </c>
       <c r="J33" t="n">
-        <v>1299.216</v>
+        <v>1299.804</v>
       </c>
       <c r="K33" t="n">
-        <v>2.300000000000001</v>
+        <v>0.8999999999999986</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1708,37 +1708,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B34" t="n">
-        <v>132.9</v>
+        <v>133.4</v>
       </c>
       <c r="C34" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E34" t="n">
-        <v>11656.03315757768</v>
+        <v>11722.85012301446</v>
       </c>
       <c r="F34" t="n">
-        <v>385.1568992561879</v>
+        <v>342.4585784418523</v>
       </c>
       <c r="G34" t="n">
         <v>1300</v>
       </c>
       <c r="H34" t="n">
-        <v>11656.03315757768</v>
+        <v>11697.30712547475</v>
       </c>
       <c r="I34" t="n">
-        <v>385.1568992561879</v>
+        <v>389.3077500106892</v>
       </c>
       <c r="J34" t="n">
-        <v>1300</v>
+        <v>1299.216</v>
       </c>
       <c r="K34" t="n">
-        <v>1.899999999999999</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1746,37 +1746,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B35" t="n">
-        <v>133.9</v>
+        <v>134.4</v>
       </c>
       <c r="C35" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E35" t="n">
-        <v>11724.79895538409</v>
+        <v>11790.47970870431</v>
       </c>
       <c r="F35" t="n">
-        <v>263.1172685944716</v>
+        <v>218.4171436733873</v>
       </c>
       <c r="G35" t="n">
         <v>1300</v>
       </c>
       <c r="H35" t="n">
-        <v>11659.06694277503</v>
+        <v>11700.40904871421</v>
       </c>
       <c r="I35" t="n">
-        <v>379.772797903465</v>
+        <v>383.6184203299159</v>
       </c>
       <c r="J35" t="n">
-        <v>1295.1</v>
+        <v>1290.396</v>
       </c>
       <c r="K35" t="n">
-        <v>3.600000000000001</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -1784,37 +1784,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B36" t="n">
-        <v>133.9</v>
+        <v>134.4</v>
       </c>
       <c r="C36" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E36" t="n">
-        <v>11698.50615034047</v>
+        <v>11751.87799727998</v>
       </c>
       <c r="F36" t="n">
-        <v>309.7794803180691</v>
+        <v>289.2176908118995</v>
       </c>
       <c r="G36" t="n">
         <v>1300</v>
       </c>
       <c r="H36" t="n">
-        <v>11659.06694277503</v>
+        <v>11700.40904871421</v>
       </c>
       <c r="I36" t="n">
-        <v>379.7727979034653</v>
+        <v>383.618420329916</v>
       </c>
       <c r="J36" t="n">
-        <v>1298.236</v>
+        <v>1296.864</v>
       </c>
       <c r="K36" t="n">
-        <v>3.399999999999999</v>
+        <v>3.099999999999998</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -1822,37 +1822,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B37" t="n">
-        <v>133.9</v>
+        <v>134.4</v>
       </c>
       <c r="C37" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="D37" t="n">
         <v>0.2</v>
       </c>
       <c r="E37" t="n">
-        <v>11672.21334529684</v>
+        <v>11713.27628585565</v>
       </c>
       <c r="F37" t="n">
-        <v>356.4416920416661</v>
+        <v>360.0182379504117</v>
       </c>
       <c r="G37" t="n">
         <v>1300</v>
       </c>
       <c r="H37" t="n">
-        <v>11659.06694277503</v>
+        <v>11700.40904871421</v>
       </c>
       <c r="I37" t="n">
-        <v>379.7727979034647</v>
+        <v>383.6184203299158</v>
       </c>
       <c r="J37" t="n">
         <v>1299.804</v>
       </c>
       <c r="K37" t="n">
-        <v>3.199999999999999</v>
+        <v>3.299999999999997</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -1860,37 +1860,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B38" t="n">
-        <v>134.9</v>
+        <v>135.4</v>
       </c>
       <c r="C38" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E38" t="n">
-        <v>11715.27542256396</v>
+        <v>11781.48030177503</v>
       </c>
       <c r="F38" t="n">
-        <v>280.0188165302029</v>
+        <v>234.9232236114331</v>
       </c>
       <c r="G38" t="n">
         <v>1300</v>
       </c>
       <c r="H38" t="n">
-        <v>11662.29708947381</v>
+        <v>11703.70244869684</v>
       </c>
       <c r="I38" t="n">
-        <v>374.0402110262938</v>
+        <v>377.5778974589713</v>
       </c>
       <c r="J38" t="n">
-        <v>1296.864</v>
+        <v>1292.944</v>
       </c>
       <c r="K38" t="n">
-        <v>3.100000000000001</v>
+        <v>1.899999999999999</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -1898,37 +1898,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B39" t="n">
-        <v>134.9</v>
+        <v>135.4</v>
       </c>
       <c r="C39" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>11688.78625601889</v>
+        <v>11742.59137523593</v>
       </c>
       <c r="F39" t="n">
-        <v>327.0295137782487</v>
+        <v>306.2505605352021</v>
       </c>
       <c r="G39" t="n">
         <v>1300</v>
       </c>
       <c r="H39" t="n">
-        <v>11662.29708947381</v>
+        <v>11703.70244869684</v>
       </c>
       <c r="I39" t="n">
-        <v>374.0402110262939</v>
+        <v>377.5778974589714</v>
       </c>
       <c r="J39" t="n">
-        <v>1299.216</v>
+        <v>1298.236</v>
       </c>
       <c r="K39" t="n">
-        <v>2.900000000000002</v>
+        <v>3.400000000000002</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -1936,37 +1936,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B40" t="n">
-        <v>134.9</v>
+        <v>135.4</v>
       </c>
       <c r="C40" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>11662.29708947381</v>
+        <v>11703.70244869684</v>
       </c>
       <c r="F40" t="n">
-        <v>374.0402110262939</v>
+        <v>377.5778974589712</v>
       </c>
       <c r="G40" t="n">
         <v>1300</v>
       </c>
       <c r="H40" t="n">
-        <v>11662.29708947381</v>
+        <v>11703.70244869684</v>
       </c>
       <c r="I40" t="n">
-        <v>374.0402110262939</v>
+        <v>377.5778974589712</v>
       </c>
       <c r="J40" t="n">
         <v>1300</v>
       </c>
       <c r="K40" t="n">
-        <v>2.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B41" t="n">
-        <v>135.9</v>
+        <v>136.4</v>
       </c>
       <c r="C41" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E41" t="n">
-        <v>11732.43741779034</v>
+        <v>11772.48089484574</v>
       </c>
       <c r="F41" t="n">
-        <v>249.5611816934411</v>
+        <v>251.4293035494793</v>
       </c>
       <c r="G41" t="n">
         <v>1300</v>
       </c>
       <c r="H41" t="n">
-        <v>11665.72359767405</v>
+        <v>11694.12861153802</v>
       </c>
       <c r="I41" t="n">
-        <v>367.9591386246748</v>
+        <v>395.1375569675311</v>
       </c>
       <c r="J41" t="n">
-        <v>1295.1</v>
+        <v>1292.944</v>
       </c>
       <c r="K41" t="n">
-        <v>1.800000000000001</v>
+        <v>0.9000000000000021</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2012,37 +2012,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B42" t="n">
-        <v>135.9</v>
+        <v>136.4</v>
       </c>
       <c r="C42" t="n">
         <v>19.4</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="E42" t="n">
-        <v>11705.75188974383</v>
+        <v>11733.30475319188</v>
       </c>
       <c r="F42" t="n">
-        <v>296.9203644659347</v>
+        <v>323.2834302585047</v>
       </c>
       <c r="G42" t="n">
         <v>1300</v>
       </c>
       <c r="H42" t="n">
-        <v>11665.72359767405</v>
+        <v>11707.18732542264</v>
       </c>
       <c r="I42" t="n">
-        <v>367.9591386246751</v>
+        <v>371.1861813978552</v>
       </c>
       <c r="J42" t="n">
-        <v>1298.236</v>
+        <v>1299.216</v>
       </c>
       <c r="K42" t="n">
-        <v>1.900000000000002</v>
+        <v>2.199999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2050,37 +2050,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B43" t="n">
-        <v>135.9</v>
+        <v>136.4</v>
       </c>
       <c r="C43" t="n">
         <v>19.4</v>
       </c>
       <c r="D43" t="n">
-        <v>0.8</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>11705.75188974383</v>
+        <v>11733.30475319188</v>
       </c>
       <c r="F43" t="n">
-        <v>296.9203644659347</v>
+        <v>323.2834302585047</v>
       </c>
       <c r="G43" t="n">
         <v>1300</v>
       </c>
       <c r="H43" t="n">
-        <v>11652.38083365079</v>
+        <v>11694.12861153802</v>
       </c>
       <c r="I43" t="n">
-        <v>391.6387300109217</v>
+        <v>395.1375569675308</v>
       </c>
       <c r="J43" t="n">
-        <v>1296.864</v>
+        <v>1298.236</v>
       </c>
       <c r="K43" t="n">
-        <v>1.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2088,37 +2088,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B44" t="n">
-        <v>135.9</v>
+        <v>136.4</v>
       </c>
       <c r="C44" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>11679.06636169731</v>
+        <v>11694.12861153802</v>
       </c>
       <c r="F44" t="n">
-        <v>344.2795472384282</v>
+        <v>395.1375569675311</v>
       </c>
       <c r="G44" t="n">
         <v>1300</v>
       </c>
       <c r="H44" t="n">
-        <v>11665.72359767405</v>
+        <v>11694.12861153802</v>
       </c>
       <c r="I44" t="n">
-        <v>367.9591386246749</v>
+        <v>395.1375569675311</v>
       </c>
       <c r="J44" t="n">
-        <v>1299.804</v>
+        <v>1300</v>
       </c>
       <c r="K44" t="n">
-        <v>1.900000000000002</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2126,37 +2126,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B45" t="n">
-        <v>136.9</v>
+        <v>137.4</v>
       </c>
       <c r="C45" t="n">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="D45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>11802.94484468508</v>
+      </c>
+      <c r="F45" t="n">
+        <v>195.5544669932424</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H45" t="n">
+        <v>11697.70922663542</v>
+      </c>
+      <c r="I45" t="n">
+        <v>388.5702443113298</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K45" t="n">
         <v>1</v>
-      </c>
-      <c r="E45" t="n">
-        <v>11723.11024647166</v>
-      </c>
-      <c r="F45" t="n">
-        <v>266.114244104725</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H45" t="n">
-        <v>11655.90552260174</v>
-      </c>
-      <c r="I45" t="n">
-        <v>385.3834148470789</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1295.1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>3.100000000000001</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2164,37 +2164,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B46" t="n">
-        <v>136.9</v>
+        <v>137.4</v>
       </c>
       <c r="C46" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>11696.22835692369</v>
+        <v>11763.48148791646</v>
       </c>
       <c r="F46" t="n">
-        <v>313.8219124016664</v>
+        <v>267.9353834875251</v>
       </c>
       <c r="G46" t="n">
         <v>1300</v>
       </c>
       <c r="H46" t="n">
-        <v>11669.34646737573</v>
+        <v>11697.70922663542</v>
       </c>
       <c r="I46" t="n">
-        <v>361.5295806986078</v>
+        <v>388.5702443113296</v>
       </c>
       <c r="J46" t="n">
-        <v>1299.216</v>
+        <v>1295.1</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5</v>
+        <v>2.400000000000002</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2202,37 +2202,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B47" t="n">
-        <v>136.9</v>
+        <v>137.4</v>
       </c>
       <c r="C47" t="n">
         <v>19.4</v>
       </c>
       <c r="D47" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="E47" t="n">
-        <v>11696.22835692369</v>
+        <v>11724.01813114784</v>
       </c>
       <c r="F47" t="n">
-        <v>313.8219124016664</v>
+        <v>340.3162999818078</v>
       </c>
       <c r="G47" t="n">
         <v>1300</v>
       </c>
       <c r="H47" t="n">
-        <v>11655.90552260174</v>
+        <v>11697.70922663542</v>
       </c>
       <c r="I47" t="n">
-        <v>385.3834148470789</v>
+        <v>388.5702443113294</v>
       </c>
       <c r="J47" t="n">
-        <v>1298.236</v>
+        <v>1299.216</v>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>2.699999999999999</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2240,37 +2240,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B48" t="n">
-        <v>136.9</v>
+        <v>138.4</v>
       </c>
       <c r="C48" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="E48" t="n">
-        <v>11669.34646737573</v>
+        <v>11794.23265287056</v>
       </c>
       <c r="F48" t="n">
-        <v>361.5295806986082</v>
+        <v>211.5337571460318</v>
       </c>
       <c r="G48" t="n">
         <v>1300</v>
       </c>
       <c r="H48" t="n">
-        <v>11669.34646737573</v>
+        <v>11701.48131847599</v>
       </c>
       <c r="I48" t="n">
-        <v>361.5295806986082</v>
+        <v>381.6517384649571</v>
       </c>
       <c r="J48" t="n">
-        <v>1300</v>
+        <v>1290.396</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6000000000000014</v>
+        <v>1.199999999999999</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2278,37 +2278,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B49" t="n">
-        <v>136.9</v>
+        <v>138.4</v>
       </c>
       <c r="C49" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E49" t="n">
-        <v>11669.34646737573</v>
+        <v>11754.48208098718</v>
       </c>
       <c r="F49" t="n">
-        <v>361.5295806986082</v>
+        <v>284.4414634255713</v>
       </c>
       <c r="G49" t="n">
         <v>1300</v>
       </c>
       <c r="H49" t="n">
-        <v>11655.90552260174</v>
+        <v>11701.48131847599</v>
       </c>
       <c r="I49" t="n">
-        <v>385.3834148470789</v>
+        <v>381.6517384649574</v>
       </c>
       <c r="J49" t="n">
-        <v>1299.804</v>
+        <v>1296.864</v>
       </c>
       <c r="K49" t="n">
-        <v>2.600000000000001</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2316,37 +2316,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121</v>
+        <v>118.6</v>
       </c>
       <c r="B50" t="n">
-        <v>131.9</v>
+        <v>138.4</v>
       </c>
       <c r="C50" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="D50" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E50" t="n">
-        <v>11627.74285397115</v>
+        <v>11714.73150910379</v>
       </c>
       <c r="F50" t="n">
-        <v>283.8194126446942</v>
+        <v>357.3491697051104</v>
       </c>
       <c r="G50" t="n">
         <v>1300</v>
       </c>
       <c r="H50" t="n">
-        <v>11573.39603630664</v>
+        <v>11701.48131847599</v>
       </c>
       <c r="I50" t="n">
-        <v>374.2677062147812</v>
+        <v>381.6517384649568</v>
       </c>
       <c r="J50" t="n">
-        <v>1296.864</v>
+        <v>1299.804</v>
       </c>
       <c r="K50" t="n">
-        <v>1.100000000000001</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2354,37 +2354,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121</v>
+        <v>118.6</v>
       </c>
       <c r="B51" t="n">
-        <v>132.9</v>
+        <v>139.4</v>
       </c>
       <c r="C51" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E51" t="n">
-        <v>11644.71850892018</v>
+        <v>11785.52046105604</v>
       </c>
       <c r="F51" t="n">
-        <v>255.5671784135525</v>
+        <v>227.5130472988208</v>
       </c>
       <c r="G51" t="n">
         <v>1300</v>
       </c>
       <c r="H51" t="n">
-        <v>11576.26994876464</v>
+        <v>11692.09895806036</v>
       </c>
       <c r="I51" t="n">
-        <v>369.4847126768632</v>
+        <v>398.8602047833453</v>
       </c>
       <c r="J51" t="n">
-        <v>1295.1</v>
+        <v>1290.396</v>
       </c>
       <c r="K51" t="n">
-        <v>1.899999999999999</v>
+        <v>0.3000000000000007</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2392,37 +2392,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121</v>
+        <v>118.6</v>
       </c>
       <c r="B52" t="n">
-        <v>132.9</v>
+        <v>139.4</v>
       </c>
       <c r="C52" t="n">
-        <v>20.2</v>
+        <v>18.8</v>
       </c>
       <c r="D52" t="n">
         <v>0.6000000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>11617.33908485797</v>
+        <v>11745.48267405789</v>
       </c>
       <c r="F52" t="n">
-        <v>301.1341921188764</v>
+        <v>300.9475433636176</v>
       </c>
       <c r="G52" t="n">
         <v>1300</v>
       </c>
       <c r="H52" t="n">
-        <v>11576.26994876464</v>
+        <v>11705.44488705974</v>
       </c>
       <c r="I52" t="n">
-        <v>369.484712676863</v>
+        <v>374.382039428414</v>
       </c>
       <c r="J52" t="n">
         <v>1298.236</v>
       </c>
       <c r="K52" t="n">
-        <v>1.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2430,37 +2430,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121</v>
+        <v>118.6</v>
       </c>
       <c r="B53" t="n">
-        <v>132.9</v>
+        <v>139.4</v>
       </c>
       <c r="C53" t="n">
-        <v>20.6</v>
+        <v>18.8</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E53" t="n">
-        <v>11589.95966079575</v>
+        <v>11745.48267405789</v>
       </c>
       <c r="F53" t="n">
-        <v>346.7012058242012</v>
+        <v>300.9475433636176</v>
       </c>
       <c r="G53" t="n">
         <v>1300</v>
       </c>
       <c r="H53" t="n">
-        <v>11576.26994876464</v>
+        <v>11692.09895806036</v>
       </c>
       <c r="I53" t="n">
-        <v>369.4847126768633</v>
+        <v>398.860204783346</v>
       </c>
       <c r="J53" t="n">
-        <v>1299.804</v>
+        <v>1296.864</v>
       </c>
       <c r="K53" t="n">
-        <v>0.7999999999999972</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2468,37 +2468,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121</v>
+        <v>118.6</v>
       </c>
       <c r="B54" t="n">
-        <v>133.9</v>
+        <v>139.4</v>
       </c>
       <c r="C54" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="D54" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>11634.52075503697</v>
+        <v>11705.44488705974</v>
       </c>
       <c r="F54" t="n">
-        <v>272.5390909674543</v>
+        <v>374.3820394284135</v>
       </c>
       <c r="G54" t="n">
         <v>1300</v>
       </c>
       <c r="H54" t="n">
-        <v>11579.3498764526</v>
+        <v>11705.44488705974</v>
       </c>
       <c r="I54" t="n">
-        <v>364.3588522186647</v>
+        <v>374.3820394284135</v>
       </c>
       <c r="J54" t="n">
-        <v>1296.864</v>
+        <v>1300</v>
       </c>
       <c r="K54" t="n">
-        <v>1.099999999999998</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2506,37 +2506,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121</v>
+        <v>120.2</v>
       </c>
       <c r="B55" t="n">
-        <v>133.9</v>
+        <v>129.4</v>
       </c>
       <c r="C55" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="E55" t="n">
-        <v>11606.93531574478</v>
+        <v>11737.23884677732</v>
       </c>
       <c r="F55" t="n">
-        <v>318.4489715930595</v>
+        <v>169.6408918325019</v>
       </c>
       <c r="G55" t="n">
         <v>1300</v>
       </c>
       <c r="H55" t="n">
-        <v>11579.3498764526</v>
+        <v>11620.07544080821</v>
       </c>
       <c r="I55" t="n">
-        <v>364.3588522186644</v>
+        <v>370.9477787035589</v>
       </c>
       <c r="J55" t="n">
-        <v>1299.216</v>
+        <v>1284.124</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7999999999999972</v>
+        <v>2.300000000000001</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -2544,37 +2544,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121</v>
+        <v>120.2</v>
       </c>
       <c r="B56" t="n">
-        <v>133.9</v>
+        <v>129.4</v>
       </c>
       <c r="C56" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E56" t="n">
-        <v>11579.3498764526</v>
+        <v>11698.18437812095</v>
       </c>
       <c r="F56" t="n">
-        <v>364.3588522186647</v>
+        <v>236.7431874561876</v>
       </c>
       <c r="G56" t="n">
         <v>1300</v>
       </c>
       <c r="H56" t="n">
-        <v>11579.3498764526</v>
+        <v>11620.07544080821</v>
       </c>
       <c r="I56" t="n">
-        <v>364.3588522186647</v>
+        <v>370.9477787035588</v>
       </c>
       <c r="J56" t="n">
-        <v>1300</v>
+        <v>1292.944</v>
       </c>
       <c r="K56" t="n">
-        <v>0.6999999999999993</v>
+        <v>2.5</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2582,37 +2582,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121</v>
+        <v>120.2</v>
       </c>
       <c r="B57" t="n">
-        <v>134.9</v>
+        <v>129.4</v>
       </c>
       <c r="C57" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>11652.11445567589</v>
+        <v>11659.12990946458</v>
       </c>
       <c r="F57" t="n">
-        <v>243.2582559754701</v>
+        <v>303.8454830798732</v>
       </c>
       <c r="G57" t="n">
         <v>1300</v>
       </c>
       <c r="H57" t="n">
-        <v>11582.63581937053</v>
+        <v>11620.07544080821</v>
       </c>
       <c r="I57" t="n">
-        <v>358.8901248401851</v>
+        <v>370.947778703559</v>
       </c>
       <c r="J57" t="n">
-        <v>1295.1</v>
+        <v>1298.236</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5999999999999979</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -2620,37 +2620,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121</v>
+        <v>120.2</v>
       </c>
       <c r="B58" t="n">
-        <v>134.9</v>
+        <v>129.4</v>
       </c>
       <c r="C58" t="n">
-        <v>19.8</v>
+        <v>21.2</v>
       </c>
       <c r="D58" t="n">
-        <v>0.6000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>11624.32300115375</v>
+        <v>11620.07544080821</v>
       </c>
       <c r="F58" t="n">
-        <v>289.5110035213561</v>
+        <v>370.9477787035589</v>
       </c>
       <c r="G58" t="n">
         <v>1300</v>
       </c>
       <c r="H58" t="n">
-        <v>11582.63581937053</v>
+        <v>11620.07544080821</v>
       </c>
       <c r="I58" t="n">
-        <v>358.8901248401852</v>
+        <v>370.9477787035589</v>
       </c>
       <c r="J58" t="n">
-        <v>1298.236</v>
+        <v>1300</v>
       </c>
       <c r="K58" t="n">
-        <v>0.3999999999999986</v>
+        <v>1.5</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -2658,37 +2658,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121</v>
+        <v>120.2</v>
       </c>
       <c r="B59" t="n">
-        <v>134.9</v>
+        <v>130.4</v>
       </c>
       <c r="C59" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="E59" t="n">
-        <v>11596.5315466316</v>
+        <v>11727.4802598127</v>
       </c>
       <c r="F59" t="n">
-        <v>335.7637510672421</v>
+        <v>186.4078229904039</v>
       </c>
       <c r="G59" t="n">
         <v>1300</v>
       </c>
       <c r="H59" t="n">
-        <v>11582.63581937053</v>
+        <v>11622.53017814776</v>
       </c>
       <c r="I59" t="n">
-        <v>358.890124840185</v>
+        <v>366.730117670025</v>
       </c>
       <c r="J59" t="n">
-        <v>1299.804</v>
+        <v>1287.456</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1000000000000014</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -2696,37 +2696,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121</v>
+        <v>120.2</v>
       </c>
       <c r="B60" t="n">
-        <v>135.9</v>
+        <v>130.4</v>
       </c>
       <c r="C60" t="n">
         <v>19.4</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E60" t="n">
-        <v>11642.12271702264</v>
+        <v>11727.4802598127</v>
       </c>
       <c r="F60" t="n">
-        <v>259.8873016090911</v>
+        <v>186.4078229904039</v>
       </c>
       <c r="G60" t="n">
         <v>1300</v>
       </c>
       <c r="H60" t="n">
-        <v>11572.12904264236</v>
+        <v>11609.41141793965</v>
       </c>
       <c r="I60" t="n">
-        <v>376.3763377745082</v>
+        <v>389.2704045049776</v>
       </c>
       <c r="J60" t="n">
-        <v>1295.1</v>
+        <v>1284.124</v>
       </c>
       <c r="K60" t="n">
-        <v>2.300000000000001</v>
+        <v>0.7999999999999972</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -2734,37 +2734,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121</v>
+        <v>120.2</v>
       </c>
       <c r="B61" t="n">
-        <v>136.9</v>
+        <v>130.4</v>
       </c>
       <c r="C61" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>11632.13097836938</v>
+        <v>11688.12397918835</v>
       </c>
       <c r="F61" t="n">
-        <v>276.5163472427121</v>
+        <v>254.0286834952617</v>
       </c>
       <c r="G61" t="n">
         <v>1300</v>
       </c>
       <c r="H61" t="n">
-        <v>11575.72400840523</v>
+        <v>11622.53017814776</v>
       </c>
       <c r="I61" t="n">
-        <v>370.3933100156075</v>
+        <v>366.7301176700248</v>
       </c>
       <c r="J61" t="n">
-        <v>1296.864</v>
+        <v>1295.1</v>
       </c>
       <c r="K61" t="n">
-        <v>1.899999999999999</v>
+        <v>1.699999999999999</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -2772,37 +2772,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121</v>
+        <v>120.2</v>
       </c>
       <c r="B62" t="n">
-        <v>136.9</v>
+        <v>130.4</v>
       </c>
       <c r="C62" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="D62" t="n">
         <v>0.4</v>
       </c>
       <c r="E62" t="n">
-        <v>11603.92749338731</v>
+        <v>11648.767698564</v>
       </c>
       <c r="F62" t="n">
-        <v>323.4548286291597</v>
+        <v>321.6495440001199</v>
       </c>
       <c r="G62" t="n">
         <v>1300</v>
       </c>
       <c r="H62" t="n">
-        <v>11575.72400840524</v>
+        <v>11622.53017814776</v>
       </c>
       <c r="I62" t="n">
-        <v>370.3933100156072</v>
+        <v>366.730117670025</v>
       </c>
       <c r="J62" t="n">
         <v>1299.216</v>
       </c>
       <c r="K62" t="n">
-        <v>1.5</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -2810,39 +2810,2509 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121</v>
+        <v>120.2</v>
       </c>
       <c r="B63" t="n">
-        <v>136.9</v>
+        <v>131.4</v>
       </c>
       <c r="C63" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="E63" t="n">
-        <v>11575.72400840523</v>
+        <v>11717.72167284807</v>
       </c>
       <c r="F63" t="n">
-        <v>370.3933100156073</v>
+        <v>203.1747541483055</v>
       </c>
       <c r="G63" t="n">
         <v>1300</v>
       </c>
       <c r="H63" t="n">
-        <v>11575.72400840523</v>
+        <v>11625.18612346597</v>
       </c>
       <c r="I63" t="n">
-        <v>370.3933100156073</v>
+        <v>362.1667467157089</v>
       </c>
       <c r="J63" t="n">
-        <v>1300</v>
+        <v>1290.396</v>
       </c>
       <c r="K63" t="n">
-        <v>1.299999999999997</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="L63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B64" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="C64" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E64" t="n">
+        <v>11717.72167284807</v>
+      </c>
+      <c r="F64" t="n">
+        <v>203.1747541483055</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H64" t="n">
+        <v>11611.96675926853</v>
+      </c>
+      <c r="I64" t="n">
+        <v>384.8798885110525</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B65" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="C65" t="n">
+        <v>20</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E65" t="n">
+        <v>11678.06358025574</v>
+      </c>
+      <c r="F65" t="n">
+        <v>271.3141795343358</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H65" t="n">
+        <v>11625.18612346597</v>
+      </c>
+      <c r="I65" t="n">
+        <v>362.1667467157093</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1296.864</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B66" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="C66" t="n">
+        <v>20</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>11678.06358025574</v>
+      </c>
+      <c r="F66" t="n">
+        <v>271.3141795343358</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H66" t="n">
+        <v>11611.96675926853</v>
+      </c>
+      <c r="I66" t="n">
+        <v>384.8798885110526</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.6999999999999993</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B67" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="C67" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>11638.40548766341</v>
+      </c>
+      <c r="F67" t="n">
+        <v>339.4536049203662</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H67" t="n">
+        <v>11625.18612346597</v>
+      </c>
+      <c r="I67" t="n">
+        <v>362.1667467157095</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1299.804</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.6999999999999993</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B68" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="C68" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="n">
+        <v>11747.92299044375</v>
+      </c>
+      <c r="F68" t="n">
+        <v>151.2836950390056</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H68" t="n">
+        <v>11614.72330857606</v>
+      </c>
+      <c r="I68" t="n">
+        <v>380.1436625963466</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1.900000000000002</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B69" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="C69" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E69" t="n">
+        <v>11707.96308588344</v>
+      </c>
+      <c r="F69" t="n">
+        <v>219.9416853062075</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H69" t="n">
+        <v>11614.72330857606</v>
+      </c>
+      <c r="I69" t="n">
+        <v>380.1436625963461</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1290.396</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.199999999999999</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B70" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="C70" t="n">
+        <v>20</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>11668.00318132314</v>
+      </c>
+      <c r="F70" t="n">
+        <v>288.59967557341</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H70" t="n">
+        <v>11614.72330857606</v>
+      </c>
+      <c r="I70" t="n">
+        <v>380.1436625963465</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1296.864</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B71" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="C71" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E71" t="n">
+        <v>11738.4662154471</v>
+      </c>
+      <c r="F71" t="n">
+        <v>167.5320613157351</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H71" t="n">
+        <v>11617.68106586225</v>
+      </c>
+      <c r="I71" t="n">
+        <v>375.0617267608587</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1284.124</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B72" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="C72" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>11698.20449891882</v>
+      </c>
+      <c r="F72" t="n">
+        <v>236.7086164641096</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H72" t="n">
+        <v>11617.68106586225</v>
+      </c>
+      <c r="I72" t="n">
+        <v>375.0617267608585</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1292.944</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3.300000000000001</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B73" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="C73" t="n">
+        <v>20</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="E73" t="n">
+        <v>11657.94278239053</v>
+      </c>
+      <c r="F73" t="n">
+        <v>305.8851716124841</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H73" t="n">
+        <v>11617.68106586225</v>
+      </c>
+      <c r="I73" t="n">
+        <v>375.0617267608588</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1298.236</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B74" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>11617.68106586225</v>
+      </c>
+      <c r="F74" t="n">
+        <v>375.0617267608586</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H74" t="n">
+        <v>11617.68106586225</v>
+      </c>
+      <c r="I74" t="n">
+        <v>375.0617267608586</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2.099999999999998</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B75" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="C75" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11729.00944045045</v>
+      </c>
+      <c r="F75" t="n">
+        <v>183.780427592465</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H75" t="n">
+        <v>11620.84003112709</v>
+      </c>
+      <c r="I75" t="n">
+        <v>369.6340810045898</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B76" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="C76" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E76" t="n">
+        <v>11729.00944045045</v>
+      </c>
+      <c r="F76" t="n">
+        <v>183.780427592465</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H76" t="n">
+        <v>11607.31885496167</v>
+      </c>
+      <c r="I76" t="n">
+        <v>392.8657876811053</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1284.124</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B77" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="C77" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>11688.44591195419</v>
+      </c>
+      <c r="F77" t="n">
+        <v>253.4755476220112</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H77" t="n">
+        <v>11620.84003112709</v>
+      </c>
+      <c r="I77" t="n">
+        <v>369.6340810045891</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B78" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="C78" t="n">
+        <v>20</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E78" t="n">
+        <v>11647.88238345793</v>
+      </c>
+      <c r="F78" t="n">
+        <v>323.1706676515582</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H78" t="n">
+        <v>11620.84003112709</v>
+      </c>
+      <c r="I78" t="n">
+        <v>369.6340810045892</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1299.216</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B79" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="C79" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E79" t="n">
+        <v>11719.5526654538</v>
+      </c>
+      <c r="F79" t="n">
+        <v>200.0287938691945</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H79" t="n">
+        <v>11624.20020437058</v>
+      </c>
+      <c r="I79" t="n">
+        <v>363.8607253275386</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1290.396</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B80" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="C80" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E80" t="n">
+        <v>11719.5526654538</v>
+      </c>
+      <c r="F80" t="n">
+        <v>200.0287938691945</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H80" t="n">
+        <v>11610.57842421583</v>
+      </c>
+      <c r="I80" t="n">
+        <v>387.2652869644452</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2.099999999999998</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B81" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="C81" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E81" t="n">
+        <v>11678.68732498956</v>
+      </c>
+      <c r="F81" t="n">
+        <v>270.2424787799132</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H81" t="n">
+        <v>11624.20020437058</v>
+      </c>
+      <c r="I81" t="n">
+        <v>363.8607253275386</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1296.864</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1.300000000000001</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B82" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="C82" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>11678.68732498956</v>
+      </c>
+      <c r="F82" t="n">
+        <v>270.2424787799132</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H82" t="n">
+        <v>11610.57842421583</v>
+      </c>
+      <c r="I82" t="n">
+        <v>387.2652869644448</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.6999999999999993</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B83" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="C83" t="n">
+        <v>20</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>11637.82198452532</v>
+      </c>
+      <c r="F83" t="n">
+        <v>340.4561636906324</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H83" t="n">
+        <v>11624.20020437058</v>
+      </c>
+      <c r="I83" t="n">
+        <v>363.8607253275386</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1299.804</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1.099999999999998</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B84" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C84" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="n">
+        <v>11751.26304288937</v>
+      </c>
+      <c r="F84" t="n">
+        <v>145.5449103540327</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H84" t="n">
+        <v>11614.03920144865</v>
+      </c>
+      <c r="I84" t="n">
+        <v>381.3190763270034</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B85" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C85" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E85" t="n">
+        <v>11710.09589045716</v>
+      </c>
+      <c r="F85" t="n">
+        <v>216.277160145924</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H85" t="n">
+        <v>11614.03920144865</v>
+      </c>
+      <c r="I85" t="n">
+        <v>381.3190763270032</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1290.396</v>
+      </c>
+      <c r="K85" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B86" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C86" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="E86" t="n">
+        <v>11668.92873802494</v>
+      </c>
+      <c r="F86" t="n">
+        <v>287.0094099378152</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H86" t="n">
+        <v>11627.76158559272</v>
+      </c>
+      <c r="I86" t="n">
+        <v>357.7416597297066</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1298.236</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.09999999999999787</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B87" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C87" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E87" t="n">
+        <v>11668.92873802494</v>
+      </c>
+      <c r="F87" t="n">
+        <v>287.0094099378152</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H87" t="n">
+        <v>11614.03920144865</v>
+      </c>
+      <c r="I87" t="n">
+        <v>381.3190763270036</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1296.864</v>
+      </c>
+      <c r="K87" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B88" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C88" t="n">
+        <v>20</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>11627.76158559272</v>
+      </c>
+      <c r="F88" t="n">
+        <v>357.7416597297065</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H88" t="n">
+        <v>11627.76158559272</v>
+      </c>
+      <c r="I88" t="n">
+        <v>357.7416597297065</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.09999999999999787</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B89" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C89" t="n">
+        <v>20</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E89" t="n">
+        <v>11627.76158559272</v>
+      </c>
+      <c r="F89" t="n">
+        <v>357.7416597297065</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H89" t="n">
+        <v>11614.03920144864</v>
+      </c>
+      <c r="I89" t="n">
+        <v>381.3190763270035</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1299.804</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B90" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="C90" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E90" t="n">
+        <v>11742.1080798607</v>
+      </c>
+      <c r="F90" t="n">
+        <v>161.2747117495901</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H90" t="n">
+        <v>11617.70118666011</v>
+      </c>
+      <c r="I90" t="n">
+        <v>375.0271557687804</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1284.124</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B91" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="C91" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>11700.63911546051</v>
+      </c>
+      <c r="F91" t="n">
+        <v>232.5255264226539</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H91" t="n">
+        <v>11617.70118666012</v>
+      </c>
+      <c r="I91" t="n">
+        <v>375.0271557687806</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1292.944</v>
+      </c>
+      <c r="K91" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B92" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="C92" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="E92" t="n">
+        <v>11659.17015106031</v>
+      </c>
+      <c r="F92" t="n">
+        <v>303.7763410957168</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H92" t="n">
+        <v>11617.70118666011</v>
+      </c>
+      <c r="I92" t="n">
+        <v>375.0271557687804</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1298.236</v>
+      </c>
+      <c r="K92" t="n">
+        <v>2.800000000000001</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B93" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="C93" t="n">
+        <v>20</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>11617.70118666011</v>
+      </c>
+      <c r="F93" t="n">
+        <v>375.0271557687806</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H93" t="n">
+        <v>11617.70118666011</v>
+      </c>
+      <c r="I93" t="n">
+        <v>375.0271557687806</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B94" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="C94" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E94" t="n">
+        <v>11732.95311683203</v>
+      </c>
+      <c r="F94" t="n">
+        <v>177.0045131451475</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H94" t="n">
+        <v>11621.56437985024</v>
+      </c>
+      <c r="I94" t="n">
+        <v>368.389525289776</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B95" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="C95" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E95" t="n">
+        <v>11732.95311683203</v>
+      </c>
+      <c r="F95" t="n">
+        <v>177.0045131451475</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H95" t="n">
+        <v>11607.64078772751</v>
+      </c>
+      <c r="I95" t="n">
+        <v>392.3126518078545</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1284.124</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1.200000000000003</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B96" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="C96" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>11691.18234046386</v>
+      </c>
+      <c r="F96" t="n">
+        <v>248.7738926993834</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H96" t="n">
+        <v>11621.56437985023</v>
+      </c>
+      <c r="I96" t="n">
+        <v>368.3895252897761</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B97" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="C97" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E97" t="n">
+        <v>11649.41156409568</v>
+      </c>
+      <c r="F97" t="n">
+        <v>320.5432722536189</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H97" t="n">
+        <v>11621.56437985024</v>
+      </c>
+      <c r="I97" t="n">
+        <v>368.3895252897757</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1299.216</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B98" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="C98" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E98" t="n">
+        <v>11723.79815380336</v>
+      </c>
+      <c r="F98" t="n">
+        <v>192.7343145407049</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H98" t="n">
+        <v>11611.60458490696</v>
+      </c>
+      <c r="I98" t="n">
+        <v>385.5021663684594</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K98" t="n">
+        <v>2.900000000000002</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B99" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="C99" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E99" t="n">
+        <v>11681.72556546721</v>
+      </c>
+      <c r="F99" t="n">
+        <v>265.0222589761129</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H99" t="n">
+        <v>11625.62878101901</v>
+      </c>
+      <c r="I99" t="n">
+        <v>361.4061848899901</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1296.864</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B100" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="C100" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>11681.72556546721</v>
+      </c>
+      <c r="F100" t="n">
+        <v>265.0222589761129</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H100" t="n">
+        <v>11611.60458490696</v>
+      </c>
+      <c r="I100" t="n">
+        <v>385.5021663684593</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="B101" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="C101" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E101" t="n">
+        <v>11639.65297713106</v>
+      </c>
+      <c r="F101" t="n">
+        <v>337.3102034115204</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H101" t="n">
+        <v>11625.62878101901</v>
+      </c>
+      <c r="I101" t="n">
+        <v>361.4061848899896</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1299.804</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B102" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="C102" t="n">
+        <v>20</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E102" t="n">
+        <v>11636.2384012546</v>
+      </c>
+      <c r="F102" t="n">
+        <v>199.5222894500039</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H102" t="n">
+        <v>11527.13747335497</v>
+      </c>
+      <c r="I102" t="n">
+        <v>375.4840726060044</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B103" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="C103" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" t="n">
+        <v>11666.92830678432</v>
+      </c>
+      <c r="F103" t="n">
+        <v>150.0245390104487</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H103" t="n">
+        <v>11529.49823531879</v>
+      </c>
+      <c r="I103" t="n">
+        <v>371.6765533414228</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K103" t="n">
+        <v>3.300000000000001</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B104" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="C104" t="n">
+        <v>20</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E104" t="n">
+        <v>11625.69928534466</v>
+      </c>
+      <c r="F104" t="n">
+        <v>216.5201433097409</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H104" t="n">
+        <v>11529.49823531879</v>
+      </c>
+      <c r="I104" t="n">
+        <v>371.6765533414226</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1290.396</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1.699999999999999</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B105" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="C105" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E105" t="n">
+        <v>11656.70536435169</v>
+      </c>
+      <c r="F105" t="n">
+        <v>166.5124572543937</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H105" t="n">
+        <v>11532.06977960081</v>
+      </c>
+      <c r="I105" t="n">
+        <v>367.5290769996468</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1284.124</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B106" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="C106" t="n">
+        <v>20</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E106" t="n">
+        <v>11615.16016943473</v>
+      </c>
+      <c r="F106" t="n">
+        <v>233.5179971694783</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H106" t="n">
+        <v>11532.06977960082</v>
+      </c>
+      <c r="I106" t="n">
+        <v>367.529076999647</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1292.944</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B107" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="C107" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E107" t="n">
+        <v>11646.48242191905</v>
+      </c>
+      <c r="F107" t="n">
+        <v>183.0003754983391</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H107" t="n">
+        <v>11534.85210620104</v>
+      </c>
+      <c r="I107" t="n">
+        <v>363.0416435806765</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B108" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="C108" t="n">
+        <v>20</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>11604.6210535248</v>
+      </c>
+      <c r="F108" t="n">
+        <v>250.5158510292158</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H108" t="n">
+        <v>11534.85210620104</v>
+      </c>
+      <c r="I108" t="n">
+        <v>363.0416435806766</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B109" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="C109" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="n">
+        <v>11678.43702135797</v>
+      </c>
+      <c r="F109" t="n">
+        <v>131.4628825956161</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H109" t="n">
+        <v>11537.84521511946</v>
+      </c>
+      <c r="I109" t="n">
+        <v>358.2142530845114</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B110" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="C110" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E110" t="n">
+        <v>11636.25947948642</v>
+      </c>
+      <c r="F110" t="n">
+        <v>199.4882937422844</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H110" t="n">
+        <v>11537.84521511946</v>
+      </c>
+      <c r="I110" t="n">
+        <v>358.214253084511</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1290.396</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B111" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="C111" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" t="n">
+        <v>11668.53025240263</v>
+      </c>
+      <c r="F111" t="n">
+        <v>147.4408652237689</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H111" t="n">
+        <v>11526.88453457313</v>
+      </c>
+      <c r="I111" t="n">
+        <v>375.8920210986379</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3.599999999999998</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B112" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="C112" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E112" t="n">
+        <v>11626.03653705378</v>
+      </c>
+      <c r="F112" t="n">
+        <v>215.9762119862294</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H112" t="n">
+        <v>11526.88453457313</v>
+      </c>
+      <c r="I112" t="n">
+        <v>375.8920210986375</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1290.396</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B113" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="C113" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E113" t="n">
+        <v>11658.6234834473</v>
+      </c>
+      <c r="F113" t="n">
+        <v>163.4188478519218</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H113" t="n">
+        <v>11530.19381696885</v>
+      </c>
+      <c r="I113" t="n">
+        <v>370.5546949866804</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1284.124</v>
+      </c>
+      <c r="K113" t="n">
+        <v>3</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B114" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="C114" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E114" t="n">
+        <v>11615.81359462115</v>
+      </c>
+      <c r="F114" t="n">
+        <v>232.4641302301748</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H114" t="n">
+        <v>11530.19381696885</v>
+      </c>
+      <c r="I114" t="n">
+        <v>370.5546949866804</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1292.944</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B115" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C115" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E115" t="n">
+        <v>11648.71671449196</v>
+      </c>
+      <c r="F115" t="n">
+        <v>179.3968304800751</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H115" t="n">
+        <v>11533.71388168276</v>
+      </c>
+      <c r="I115" t="n">
+        <v>364.8774117975285</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B116" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C116" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>11605.59065218851</v>
+      </c>
+      <c r="F116" t="n">
+        <v>248.9520484741197</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H116" t="n">
+        <v>11533.71388168276</v>
+      </c>
+      <c r="I116" t="n">
+        <v>364.8774117975279</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.8999999999999986</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B117" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="C117" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E117" t="n">
+        <v>11638.80994553662</v>
+      </c>
+      <c r="F117" t="n">
+        <v>195.374813108228</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H117" t="n">
+        <v>11537.44472871488</v>
+      </c>
+      <c r="I117" t="n">
+        <v>358.8601715311809</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1290.396</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B118" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="C118" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E118" t="n">
+        <v>11638.80994553662</v>
+      </c>
+      <c r="F118" t="n">
+        <v>195.374813108228</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H118" t="n">
+        <v>11522.96398345463</v>
+      </c>
+      <c r="I118" t="n">
+        <v>382.2152227344603</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B119" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="C119" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E119" t="n">
+        <v>11595.36770975588</v>
+      </c>
+      <c r="F119" t="n">
+        <v>265.4399667180651</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H119" t="n">
+        <v>11537.44472871488</v>
+      </c>
+      <c r="I119" t="n">
+        <v>358.8601715311813</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1296.864</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B120" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="C120" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="n">
+        <v>11672.66158583933</v>
+      </c>
+      <c r="F120" t="n">
+        <v>140.7777065107516</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H120" t="n">
+        <v>11526.80022164585</v>
+      </c>
+      <c r="I120" t="n">
+        <v>376.0280039295155</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K120" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B121" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="C121" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E121" t="n">
+        <v>11628.90317658129</v>
+      </c>
+      <c r="F121" t="n">
+        <v>211.3527957363808</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H121" t="n">
+        <v>11526.80022164585</v>
+      </c>
+      <c r="I121" t="n">
+        <v>376.0280039295154</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1290.396</v>
+      </c>
+      <c r="K121" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B122" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="C122" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E122" t="n">
+        <v>11663.07099036129</v>
+      </c>
+      <c r="F122" t="n">
+        <v>156.2457535231129</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H122" t="n">
+        <v>11530.84724215526</v>
+      </c>
+      <c r="I122" t="n">
+        <v>369.5008280473768</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1284.124</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="B123" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="C123" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E123" t="n">
+        <v>11618.99640762595</v>
+      </c>
+      <c r="F123" t="n">
+        <v>227.3307783645341</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H123" t="n">
+        <v>11530.84724215526</v>
+      </c>
+      <c r="I123" t="n">
+        <v>369.5008280473767</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1292.944</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="B124" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="C124" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="n">
+        <v>11586.05719024728</v>
+      </c>
+      <c r="F124" t="n">
+        <v>144.3568276638553</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H124" t="n">
+        <v>11440.28989027278</v>
+      </c>
+      <c r="I124" t="n">
+        <v>365.4245418560053</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1.699999999999999</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="B125" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="C125" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E125" t="n">
+        <v>11575.37786388963</v>
+      </c>
+      <c r="F125" t="n">
+        <v>160.5528762111658</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H125" t="n">
+        <v>11443.19642858043</v>
+      </c>
+      <c r="I125" t="n">
+        <v>361.0165451379751</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1284.124</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="B126" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C126" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" t="n">
+        <v>11588.39122858524</v>
+      </c>
+      <c r="F126" t="n">
+        <v>140.8170727236188</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H126" t="n">
+        <v>11438.22008269006</v>
+      </c>
+      <c r="I126" t="n">
+        <v>368.5635698218762</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K126" t="n">
+        <v>2.300000000000001</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="B127" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="C127" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E127" t="n">
+        <v>11578.04219067165</v>
+      </c>
+      <c r="F127" t="n">
+        <v>156.5122125529711</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H127" t="n">
+        <v>11441.89729403382</v>
+      </c>
+      <c r="I127" t="n">
+        <v>362.9867860952768</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1284.124</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="B128" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="C128" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E128" t="n">
+        <v>11567.69315275805</v>
+      </c>
+      <c r="F128" t="n">
+        <v>172.2073523823228</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H128" t="n">
+        <v>11445.79469767363</v>
+      </c>
+      <c r="I128" t="n">
+        <v>357.0760632233718</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1287.456</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L128" t="n">
         <v>0</v>
       </c>
     </row>
